--- a/word/csvfile/协议模板（公开）.docx.xlsx
+++ b/word/csvfile/协议模板（公开）.docx.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Object\Doc2xls\word\csvfile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6394707C-4530-499F-B07D-B52FC57AE7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="协议模板（公开）.docx" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>信源系统码</t>
-  </si>
-  <si>
-    <t>信源机器码</t>
   </si>
   <si>
     <t>信宿系统码</t>
@@ -119,17 +122,37 @@
   </si>
   <si>
     <t>该时间为软件运行计时时间</t>
+  </si>
+  <si>
+    <t>信源机器码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RT3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接收组播地址</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消息ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,17 +160,30 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -177,24 +213,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +279,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -266,6 +313,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -300,9 +348,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,177 +524,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2">
         <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4">
         <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6">
         <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
         <v>17</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>